--- a/GroceryApplicationProject/src/test/resources/Testdata.xlsx
+++ b/GroceryApplicationProject/src/test/resources/Testdata.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nila\eclipse-workspace\GroceryApplicationProject\src\test\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nila\git\GroceryApplicationProject\GroceryApplicationProject\src\test\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B5C6F0A-89FB-4904-9A0D-56BDFBD53364}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80914EEC-76D8-45AB-8F32-E24584F937A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LoginPage" sheetId="1" r:id="rId1"/>
+    <sheet name="AdminPage" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -25,22 +26,88 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="22">
   <si>
     <t xml:space="preserve">admin </t>
   </si>
   <si>
     <t>admins</t>
+  </si>
+  <si>
+    <t>NewUser1</t>
+  </si>
+  <si>
+    <t>NewUser2</t>
+  </si>
+  <si>
+    <t>NewUser3</t>
+  </si>
+  <si>
+    <t>NewUser4</t>
+  </si>
+  <si>
+    <t>NewUser5</t>
+  </si>
+  <si>
+    <t>NewUser6</t>
+  </si>
+  <si>
+    <t>NewUser7</t>
+  </si>
+  <si>
+    <t>NewUser8</t>
+  </si>
+  <si>
+    <t>NewUser9</t>
+  </si>
+  <si>
+    <t>NewUser10</t>
+  </si>
+  <si>
+    <t>Password1</t>
+  </si>
+  <si>
+    <t>Password2</t>
+  </si>
+  <si>
+    <t>Password3</t>
+  </si>
+  <si>
+    <t>Password4</t>
+  </si>
+  <si>
+    <t>Password5</t>
+  </si>
+  <si>
+    <t>Password6</t>
+  </si>
+  <si>
+    <t>Password7</t>
+  </si>
+  <si>
+    <t>Password8</t>
+  </si>
+  <si>
+    <t>Password9</t>
+  </si>
+  <si>
+    <t>Password10</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -386,4 +453,98 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E3CD651-075B-4B69-AEDD-AAD01040FF7F}">
+  <dimension ref="A1:B10"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="2" max="2" width="21.46484375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A9" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" t="s">
+        <v>21</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>